--- a/Liste des tâches et Jalons.xlsx
+++ b/Liste des tâches et Jalons.xlsx
@@ -151,7 +151,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="169" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
+    <numFmt numFmtId="164" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
   </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
@@ -297,26 +297,92 @@
   <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -326,6 +392,33 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -334,99 +427,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -719,11 +719,11 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="53.33203125" customWidth="1"/>
-    <col min="5" max="5" width="10.5546875" style="27" customWidth="1"/>
-    <col min="6" max="6" width="8.88671875" style="43"/>
-    <col min="7" max="7" width="10.6640625" style="39" customWidth="1"/>
-    <col min="8" max="8" width="8.88671875" style="35"/>
-    <col min="9" max="9" width="8.88671875" style="31"/>
+    <col min="5" max="5" width="10.44140625" style="7" customWidth="1"/>
+    <col min="6" max="6" width="8.88671875" style="23"/>
+    <col min="7" max="7" width="10.6640625" style="19" customWidth="1"/>
+    <col min="8" max="8" width="8.88671875" style="15"/>
+    <col min="9" max="9" width="8.88671875" style="11"/>
     <col min="12" max="12" width="12.21875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -734,451 +734,457 @@
       <c r="C3" t="s">
         <v>36</v>
       </c>
-      <c r="E3" s="27" t="s">
+      <c r="E3" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="F3" s="43" t="s">
+      <c r="F3" s="23" t="s">
         <v>32</v>
       </c>
-      <c r="G3" s="39" t="s">
+      <c r="G3" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="H3" s="35" t="s">
+      <c r="H3" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="I3" s="31" t="s">
+      <c r="I3" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="K3" s="25" t="s">
+      <c r="K3" s="28" t="s">
         <v>38</v>
       </c>
-      <c r="L3" s="25"/>
+      <c r="L3" s="28"/>
     </row>
     <row r="4" spans="2:12" s="1" customFormat="1" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="2"/>
-      <c r="C4" s="3" t="s">
+      <c r="B4" s="29"/>
+      <c r="C4" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="E4" s="28"/>
-      <c r="F4" s="44"/>
-      <c r="G4" s="40"/>
-      <c r="H4" s="36" t="s">
-        <v>39</v>
-      </c>
-      <c r="I4" s="32"/>
-    </row>
-    <row r="5" spans="2:12" s="4" customFormat="1" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="5"/>
-      <c r="C5" s="6" t="s">
+      <c r="E4" s="8"/>
+      <c r="F4" s="24"/>
+      <c r="G4" s="20"/>
+      <c r="H4" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="I4" s="12"/>
+    </row>
+    <row r="5" spans="2:12" s="3" customFormat="1" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="30"/>
+      <c r="C5" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="E5" s="29"/>
-      <c r="F5" s="45"/>
-      <c r="G5" s="41"/>
-      <c r="H5" s="37"/>
-      <c r="I5" s="33" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="6" spans="2:12" s="4" customFormat="1" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="5"/>
-      <c r="C6" s="6" t="s">
+      <c r="E5" s="9"/>
+      <c r="F5" s="25"/>
+      <c r="G5" s="21"/>
+      <c r="H5" s="17"/>
+      <c r="I5" s="13" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12" s="3" customFormat="1" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="30"/>
+      <c r="C6" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="29"/>
-      <c r="F6" s="45"/>
-      <c r="G6" s="41"/>
-      <c r="H6" s="37"/>
-      <c r="I6" s="33" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="7" spans="2:12" s="4" customFormat="1" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="5"/>
-      <c r="C7" s="6" t="s">
+      <c r="E6" s="9"/>
+      <c r="F6" s="25"/>
+      <c r="G6" s="21"/>
+      <c r="H6" s="17"/>
+      <c r="I6" s="13" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12" s="3" customFormat="1" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="30"/>
+      <c r="C7" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E7" s="29"/>
-      <c r="F7" s="45"/>
-      <c r="G7" s="41"/>
-      <c r="H7" s="37"/>
-      <c r="I7" s="33" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="8" spans="2:12" s="4" customFormat="1" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="5"/>
-      <c r="C8" s="6" t="s">
+      <c r="E7" s="9"/>
+      <c r="F7" s="25"/>
+      <c r="G7" s="21"/>
+      <c r="H7" s="17"/>
+      <c r="I7" s="13" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12" s="3" customFormat="1" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="30"/>
+      <c r="C8" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="E8" s="29"/>
-      <c r="F8" s="45"/>
-      <c r="G8" s="41"/>
-      <c r="H8" s="37"/>
-      <c r="I8" s="33" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="9" spans="2:12" s="4" customFormat="1" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="5"/>
-      <c r="C9" s="6" t="s">
+      <c r="E8" s="9"/>
+      <c r="F8" s="25"/>
+      <c r="G8" s="21"/>
+      <c r="H8" s="17"/>
+      <c r="I8" s="13" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="9" spans="2:12" s="3" customFormat="1" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="30"/>
+      <c r="C9" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="E9" s="29"/>
-      <c r="F9" s="45"/>
-      <c r="G9" s="41" t="s">
-        <v>39</v>
-      </c>
-      <c r="H9" s="37"/>
-      <c r="I9" s="33"/>
-    </row>
-    <row r="10" spans="2:12" s="7" customFormat="1" ht="23.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B10" s="8"/>
-      <c r="C10" s="9" t="s">
+      <c r="E9" s="9"/>
+      <c r="F9" s="25"/>
+      <c r="G9" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="H9" s="17"/>
+      <c r="I9" s="13"/>
+    </row>
+    <row r="10" spans="2:12" s="5" customFormat="1" ht="23.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B10" s="31"/>
+      <c r="C10" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="E10" s="30"/>
-      <c r="F10" s="46"/>
-      <c r="G10" s="42" t="s">
-        <v>39</v>
-      </c>
-      <c r="H10" s="38"/>
-      <c r="I10" s="34"/>
-      <c r="K10" s="26">
+      <c r="E10" s="10"/>
+      <c r="F10" s="26"/>
+      <c r="G10" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="H10" s="18"/>
+      <c r="I10" s="14"/>
+      <c r="K10" s="27">
         <v>46116</v>
       </c>
-      <c r="L10" s="26"/>
-    </row>
-    <row r="11" spans="2:12" s="4" customFormat="1" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="10"/>
-      <c r="C11" s="6" t="s">
+      <c r="L10" s="27"/>
+    </row>
+    <row r="11" spans="2:12" s="3" customFormat="1" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="32"/>
+      <c r="C11" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="E11" s="29" t="s">
-        <v>39</v>
-      </c>
-      <c r="F11" s="45"/>
-      <c r="G11" s="41"/>
-      <c r="H11" s="37"/>
-      <c r="I11" s="33"/>
-    </row>
-    <row r="12" spans="2:12" s="4" customFormat="1" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="11"/>
-      <c r="C12" s="6" t="s">
+      <c r="E11" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="F11" s="25"/>
+      <c r="G11" s="21"/>
+      <c r="H11" s="17"/>
+      <c r="I11" s="13"/>
+    </row>
+    <row r="12" spans="2:12" s="3" customFormat="1" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="33"/>
+      <c r="C12" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E12" s="29" t="s">
-        <v>39</v>
-      </c>
-      <c r="F12" s="45"/>
-      <c r="G12" s="41"/>
-      <c r="H12" s="37"/>
-      <c r="I12" s="33"/>
-    </row>
-    <row r="13" spans="2:12" s="4" customFormat="1" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="11"/>
-      <c r="C13" s="6" t="s">
+      <c r="E12" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="F12" s="25"/>
+      <c r="G12" s="21"/>
+      <c r="H12" s="17"/>
+      <c r="I12" s="13"/>
+    </row>
+    <row r="13" spans="2:12" s="3" customFormat="1" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="33"/>
+      <c r="C13" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E13" s="29" t="s">
-        <v>39</v>
-      </c>
-      <c r="F13" s="45"/>
-      <c r="G13" s="41"/>
-      <c r="H13" s="37"/>
-      <c r="I13" s="33"/>
-    </row>
-    <row r="14" spans="2:12" s="4" customFormat="1" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="11"/>
-      <c r="C14" s="6" t="s">
+      <c r="E13" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="F13" s="25"/>
+      <c r="G13" s="21"/>
+      <c r="H13" s="17"/>
+      <c r="I13" s="13"/>
+    </row>
+    <row r="14" spans="2:12" s="3" customFormat="1" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="33"/>
+      <c r="C14" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E14" s="29" t="s">
-        <v>39</v>
-      </c>
-      <c r="F14" s="45"/>
-      <c r="G14" s="41"/>
-      <c r="H14" s="37"/>
-      <c r="I14" s="33"/>
-    </row>
-    <row r="15" spans="2:12" s="4" customFormat="1" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="11"/>
-      <c r="C15" s="6" t="s">
+      <c r="E14" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="F14" s="25"/>
+      <c r="G14" s="21"/>
+      <c r="H14" s="17"/>
+      <c r="I14" s="13"/>
+    </row>
+    <row r="15" spans="2:12" s="3" customFormat="1" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="33"/>
+      <c r="C15" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="E15" s="29" t="s">
-        <v>39</v>
-      </c>
-      <c r="F15" s="45"/>
-      <c r="G15" s="41"/>
-      <c r="H15" s="37"/>
-      <c r="I15" s="33"/>
-    </row>
-    <row r="16" spans="2:12" s="7" customFormat="1" ht="23.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="12"/>
-      <c r="C16" s="9" t="s">
+      <c r="E15" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="F15" s="25"/>
+      <c r="G15" s="21"/>
+      <c r="H15" s="17"/>
+      <c r="I15" s="13"/>
+    </row>
+    <row r="16" spans="2:12" s="5" customFormat="1" ht="23.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B16" s="34"/>
+      <c r="C16" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E16" s="30" t="s">
-        <v>39</v>
-      </c>
-      <c r="F16" s="46"/>
-      <c r="G16" s="42"/>
-      <c r="H16" s="38"/>
-      <c r="I16" s="34"/>
-      <c r="K16" s="26">
+      <c r="E16" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="F16" s="26"/>
+      <c r="G16" s="22"/>
+      <c r="H16" s="18"/>
+      <c r="I16" s="14"/>
+      <c r="K16" s="27">
         <v>46130</v>
       </c>
-      <c r="L16" s="26"/>
-    </row>
-    <row r="17" spans="2:12" s="4" customFormat="1" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="22"/>
-      <c r="C17" s="6" t="s">
+      <c r="L16" s="27"/>
+    </row>
+    <row r="17" spans="2:12" s="3" customFormat="1" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="35"/>
+      <c r="C17" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E17" s="29" t="s">
-        <v>39</v>
-      </c>
-      <c r="F17" s="45"/>
-      <c r="G17" s="41"/>
-      <c r="H17" s="37"/>
-      <c r="I17" s="33"/>
-    </row>
-    <row r="18" spans="2:12" s="4" customFormat="1" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="23"/>
-      <c r="C18" s="6" t="s">
+      <c r="E17" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="F17" s="25"/>
+      <c r="G17" s="21"/>
+      <c r="H17" s="17"/>
+      <c r="I17" s="13"/>
+    </row>
+    <row r="18" spans="2:12" s="3" customFormat="1" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B18" s="36"/>
+      <c r="C18" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E18" s="29" t="s">
-        <v>39</v>
-      </c>
-      <c r="F18" s="45"/>
-      <c r="G18" s="41"/>
-      <c r="H18" s="37"/>
-      <c r="I18" s="33"/>
-    </row>
-    <row r="19" spans="2:12" s="4" customFormat="1" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="23"/>
-      <c r="C19" s="6" t="s">
+      <c r="E18" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="F18" s="25"/>
+      <c r="G18" s="21"/>
+      <c r="H18" s="17"/>
+      <c r="I18" s="13"/>
+    </row>
+    <row r="19" spans="2:12" s="3" customFormat="1" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B19" s="36"/>
+      <c r="C19" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="E19" s="29" t="s">
-        <v>39</v>
-      </c>
-      <c r="F19" s="45"/>
-      <c r="G19" s="41"/>
-      <c r="H19" s="37"/>
-      <c r="I19" s="33"/>
-    </row>
-    <row r="20" spans="2:12" s="4" customFormat="1" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="23"/>
-      <c r="C20" s="6" t="s">
+      <c r="E19" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="F19" s="25"/>
+      <c r="G19" s="21"/>
+      <c r="H19" s="17"/>
+      <c r="I19" s="13"/>
+    </row>
+    <row r="20" spans="2:12" s="3" customFormat="1" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B20" s="36"/>
+      <c r="C20" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E20" s="29" t="s">
-        <v>39</v>
-      </c>
-      <c r="F20" s="45"/>
-      <c r="G20" s="41"/>
-      <c r="H20" s="37"/>
-      <c r="I20" s="33"/>
-    </row>
-    <row r="21" spans="2:12" s="7" customFormat="1" ht="23.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B21" s="24"/>
-      <c r="C21" s="9" t="s">
+      <c r="E20" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="F20" s="25"/>
+      <c r="G20" s="21"/>
+      <c r="H20" s="17"/>
+      <c r="I20" s="13"/>
+    </row>
+    <row r="21" spans="2:12" s="5" customFormat="1" ht="23.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B21" s="37"/>
+      <c r="C21" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="E21" s="30" t="s">
-        <v>39</v>
-      </c>
-      <c r="F21" s="46"/>
-      <c r="G21" s="42"/>
-      <c r="H21" s="38"/>
-      <c r="I21" s="34"/>
-      <c r="K21" s="26">
+      <c r="E21" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="F21" s="26"/>
+      <c r="G21" s="22"/>
+      <c r="H21" s="18"/>
+      <c r="I21" s="14"/>
+      <c r="K21" s="27">
         <v>46160</v>
       </c>
-      <c r="L21" s="26"/>
-    </row>
-    <row r="22" spans="2:12" s="4" customFormat="1" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="19"/>
-      <c r="C22" s="6" t="s">
+      <c r="L21" s="27"/>
+    </row>
+    <row r="22" spans="2:12" s="3" customFormat="1" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B22" s="38"/>
+      <c r="C22" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="E22" s="29" t="s">
-        <v>39</v>
-      </c>
-      <c r="F22" s="45"/>
-      <c r="G22" s="41"/>
-      <c r="H22" s="37"/>
-      <c r="I22" s="33"/>
-    </row>
-    <row r="23" spans="2:12" s="4" customFormat="1" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="20"/>
-      <c r="C23" s="6" t="s">
+      <c r="E22" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="F22" s="25"/>
+      <c r="G22" s="21"/>
+      <c r="H22" s="17"/>
+      <c r="I22" s="13"/>
+    </row>
+    <row r="23" spans="2:12" s="3" customFormat="1" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B23" s="39"/>
+      <c r="C23" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E23" s="29" t="s">
-        <v>39</v>
-      </c>
-      <c r="F23" s="45"/>
-      <c r="G23" s="41"/>
-      <c r="H23" s="37"/>
-      <c r="I23" s="33"/>
-    </row>
-    <row r="24" spans="2:12" s="4" customFormat="1" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="20"/>
-      <c r="C24" s="6" t="s">
+      <c r="E23" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="F23" s="25"/>
+      <c r="G23" s="21"/>
+      <c r="H23" s="17"/>
+      <c r="I23" s="13"/>
+    </row>
+    <row r="24" spans="2:12" s="3" customFormat="1" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B24" s="39"/>
+      <c r="C24" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E24" s="29" t="s">
-        <v>39</v>
-      </c>
-      <c r="F24" s="45"/>
-      <c r="G24" s="41"/>
-      <c r="H24" s="37"/>
-      <c r="I24" s="33"/>
-    </row>
-    <row r="25" spans="2:12" s="7" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="21"/>
-      <c r="C25" s="9" t="s">
+      <c r="E24" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="F24" s="25"/>
+      <c r="G24" s="21"/>
+      <c r="H24" s="17"/>
+      <c r="I24" s="13"/>
+    </row>
+    <row r="25" spans="2:12" s="5" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B25" s="40"/>
+      <c r="C25" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="E25" s="30" t="s">
-        <v>39</v>
-      </c>
-      <c r="F25" s="46"/>
-      <c r="G25" s="42"/>
-      <c r="H25" s="38"/>
-      <c r="I25" s="34"/>
-      <c r="K25" s="26">
+      <c r="E25" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="F25" s="26"/>
+      <c r="G25" s="22"/>
+      <c r="H25" s="18"/>
+      <c r="I25" s="14"/>
+      <c r="K25" s="27">
         <v>46179</v>
       </c>
-      <c r="L25" s="26"/>
-    </row>
-    <row r="26" spans="2:12" s="4" customFormat="1" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="16"/>
-      <c r="C26" s="6" t="s">
+      <c r="L25" s="27"/>
+    </row>
+    <row r="26" spans="2:12" s="3" customFormat="1" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B26" s="41"/>
+      <c r="C26" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E26" s="29" t="s">
-        <v>39</v>
-      </c>
-      <c r="F26" s="45"/>
-      <c r="G26" s="41"/>
-      <c r="H26" s="37"/>
-      <c r="I26" s="33"/>
-    </row>
-    <row r="27" spans="2:12" s="4" customFormat="1" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B27" s="17"/>
-      <c r="C27" s="6" t="s">
+      <c r="E26" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="F26" s="25"/>
+      <c r="G26" s="21"/>
+      <c r="H26" s="17"/>
+      <c r="I26" s="13"/>
+    </row>
+    <row r="27" spans="2:12" s="3" customFormat="1" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B27" s="42"/>
+      <c r="C27" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E27" s="29" t="s">
-        <v>39</v>
-      </c>
-      <c r="F27" s="45"/>
-      <c r="G27" s="41"/>
-      <c r="H27" s="37"/>
-      <c r="I27" s="33"/>
-    </row>
-    <row r="28" spans="2:12" s="4" customFormat="1" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B28" s="17"/>
-      <c r="C28" s="6" t="s">
+      <c r="E27" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="F27" s="25"/>
+      <c r="G27" s="21"/>
+      <c r="H27" s="17"/>
+      <c r="I27" s="13"/>
+    </row>
+    <row r="28" spans="2:12" s="3" customFormat="1" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B28" s="42"/>
+      <c r="C28" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="E28" s="29" t="s">
-        <v>39</v>
-      </c>
-      <c r="F28" s="45"/>
-      <c r="G28" s="41"/>
-      <c r="H28" s="37"/>
-      <c r="I28" s="33"/>
-    </row>
-    <row r="29" spans="2:12" s="7" customFormat="1" ht="23.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="18"/>
-      <c r="C29" s="9" t="s">
+      <c r="E28" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="F28" s="25"/>
+      <c r="G28" s="21"/>
+      <c r="H28" s="17"/>
+      <c r="I28" s="13"/>
+    </row>
+    <row r="29" spans="2:12" s="5" customFormat="1" ht="23.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B29" s="43"/>
+      <c r="C29" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="E29" s="30" t="s">
-        <v>39</v>
-      </c>
-      <c r="F29" s="46"/>
-      <c r="G29" s="42"/>
-      <c r="H29" s="38"/>
-      <c r="I29" s="34"/>
-      <c r="K29" s="26"/>
-      <c r="L29" s="26"/>
-    </row>
-    <row r="30" spans="2:12" s="4" customFormat="1" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B30" s="13"/>
-      <c r="C30" s="6" t="s">
+      <c r="E29" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="F29" s="26"/>
+      <c r="G29" s="22"/>
+      <c r="H29" s="18"/>
+      <c r="I29" s="14"/>
+      <c r="K29" s="27"/>
+      <c r="L29" s="27"/>
+    </row>
+    <row r="30" spans="2:12" s="3" customFormat="1" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B30" s="44"/>
+      <c r="C30" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="E30" s="29" t="s">
-        <v>39</v>
-      </c>
-      <c r="F30" s="45"/>
-      <c r="G30" s="41"/>
-      <c r="H30" s="37"/>
-      <c r="I30" s="33"/>
-    </row>
-    <row r="31" spans="2:12" s="4" customFormat="1" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B31" s="14"/>
-      <c r="C31" s="6" t="s">
+      <c r="E30" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="F30" s="25"/>
+      <c r="G30" s="21"/>
+      <c r="H30" s="17"/>
+      <c r="I30" s="13"/>
+    </row>
+    <row r="31" spans="2:12" s="3" customFormat="1" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B31" s="45"/>
+      <c r="C31" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="E31" s="29" t="s">
-        <v>39</v>
-      </c>
-      <c r="F31" s="45"/>
-      <c r="G31" s="41"/>
-      <c r="H31" s="37"/>
-      <c r="I31" s="33"/>
-    </row>
-    <row r="32" spans="2:12" s="4" customFormat="1" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B32" s="14"/>
-      <c r="C32" s="6" t="s">
+      <c r="E31" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="F31" s="25"/>
+      <c r="G31" s="21"/>
+      <c r="H31" s="17"/>
+      <c r="I31" s="13"/>
+    </row>
+    <row r="32" spans="2:12" s="3" customFormat="1" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B32" s="45"/>
+      <c r="C32" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E32" s="29" t="s">
-        <v>39</v>
-      </c>
-      <c r="F32" s="45"/>
-      <c r="G32" s="41"/>
-      <c r="H32" s="37"/>
-      <c r="I32" s="33"/>
-    </row>
-    <row r="33" spans="2:12" s="4" customFormat="1" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B33" s="14"/>
-      <c r="C33" s="6" t="s">
+      <c r="E32" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="F32" s="25"/>
+      <c r="G32" s="21"/>
+      <c r="H32" s="17"/>
+      <c r="I32" s="13"/>
+    </row>
+    <row r="33" spans="2:12" s="3" customFormat="1" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B33" s="45"/>
+      <c r="C33" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="E33" s="29" t="s">
-        <v>39</v>
-      </c>
-      <c r="F33" s="45"/>
-      <c r="G33" s="41"/>
-      <c r="H33" s="37"/>
-      <c r="I33" s="33"/>
-    </row>
-    <row r="34" spans="2:12" s="7" customFormat="1" ht="23.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B34" s="15"/>
-      <c r="C34" s="9" t="s">
+      <c r="E33" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="F33" s="25"/>
+      <c r="G33" s="21"/>
+      <c r="H33" s="17"/>
+      <c r="I33" s="13"/>
+    </row>
+    <row r="34" spans="2:12" s="5" customFormat="1" ht="23.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B34" s="46"/>
+      <c r="C34" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="E34" s="30" t="s">
-        <v>39</v>
-      </c>
-      <c r="F34" s="46"/>
-      <c r="G34" s="42"/>
-      <c r="H34" s="38"/>
-      <c r="I34" s="34"/>
-      <c r="K34" s="26"/>
-      <c r="L34" s="26"/>
+      <c r="E34" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="F34" s="26"/>
+      <c r="G34" s="22"/>
+      <c r="H34" s="18"/>
+      <c r="I34" s="14"/>
+      <c r="K34" s="27"/>
+      <c r="L34" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="B30:B34"/>
+    <mergeCell ref="B4:B10"/>
+    <mergeCell ref="B11:B16"/>
+    <mergeCell ref="B17:B21"/>
+    <mergeCell ref="B22:B25"/>
+    <mergeCell ref="B26:B29"/>
     <mergeCell ref="K34:L34"/>
     <mergeCell ref="K3:L3"/>
     <mergeCell ref="K10:L10"/>
@@ -1186,12 +1192,6 @@
     <mergeCell ref="K21:L21"/>
     <mergeCell ref="K25:L25"/>
     <mergeCell ref="K29:L29"/>
-    <mergeCell ref="B4:B10"/>
-    <mergeCell ref="B11:B16"/>
-    <mergeCell ref="B17:B21"/>
-    <mergeCell ref="B22:B25"/>
-    <mergeCell ref="B26:B29"/>
-    <mergeCell ref="B30:B34"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="C4" r:id="rId1" display="https://github.com/enj5/nzwi-tam/issues/22"/>
